--- a/flame-flask/static/func_case_template.xlsx
+++ b/flame-flask/static/func_case_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\BlueFlameTestPlatform\blueflame\flame-flask\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7F1D64-0BD7-4EC3-99DD-095C8D0A6027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CF532C-F014-4B28-8EC2-464795DE55E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -156,6 +156,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,7 +473,7 @@
   <cols>
     <col min="1" max="7" width="11.125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -495,10 +501,10 @@
       <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -511,8 +517,8 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
@@ -523,8 +529,8 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3"/>
@@ -535,11 +541,12 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
+  <dataConsolidate/>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{F961C31A-7DF1-4C7B-B510-64A4537383BE}">
@@ -557,10 +564,10 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{54280F5A-1049-470C-B3CF-8EB5A66C762E}">
       <formula1>"预期结果"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1" xr:uid="{07F45B15-284D-4B79-9928-951084DD206E}">
-      <formula1>"创建时间"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1" xr:uid="{31056DDF-BC0C-4CCC-B21A-3406EA1D7133}">
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="输入时间样式" error="年/月/日" promptTitle="输入时间样式" prompt="年/月/日" sqref="I1:I1048576" xr:uid="{B243B99D-3CA9-4E6E-8ADE-756E98CFD615}">
+      <formula1>45485</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="输入时间样式" error="年/月/日" promptTitle="输入时间样式" prompt="年/月/日" sqref="J1:J1048576" xr:uid="{E622156C-BFB2-482D-811F-09EDC74BA9E3}">
       <formula1>"修改时间"</formula1>
     </dataValidation>
   </dataValidations>

--- a/flame-flask/static/func_case_template.xlsx
+++ b/flame-flask/static/func_case_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\BlueFlameTestPlatform\blueflame\flame-flask\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CF532C-F014-4B28-8EC2-464795DE55E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA6FC38-5539-4E74-8881-655A9D97FB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/flame-flask/static/func_case_template.xlsx
+++ b/flame-flask/static/func_case_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\BlueFlameTestPlatform\blueflame\flame-flask\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA6FC38-5539-4E74-8881-655A9D97FB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CEF3DC-768B-4C3C-8F52-D5DB63BAEFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>用例编号</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>创建时间</t>
-  </si>
-  <si>
-    <t>修改时间</t>
   </si>
 </sst>
 </file>
@@ -468,15 +465,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="7" width="11.125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -504,11 +501,8 @@
       <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
@@ -518,9 +512,8 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -530,9 +523,8 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -542,7 +534,6 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>

--- a/flame-flask/static/func_case_template.xlsx
+++ b/flame-flask/static/func_case_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\BlueFlameTestPlatform\blueflame\flame-flask\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CEF3DC-768B-4C3C-8F52-D5DB63BAEFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178DF167-64BD-4DEC-9443-D0028B282053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/flame-flask/static/func_case_template.xlsx
+++ b/flame-flask/static/func_case_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\BlueFlameTestPlatform\blueflame\flame-flask\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7F1D64-0BD7-4EC3-99DD-095C8D0A6027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178DF167-64BD-4DEC-9443-D0028B282053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>用例编号</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>创建时间</t>
-  </si>
-  <si>
-    <t>修改时间</t>
   </si>
 </sst>
 </file>
@@ -131,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -156,6 +153,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,15 +465,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="7" width="11.125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -495,14 +498,11 @@
       <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
@@ -511,10 +511,9 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="I2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -523,10 +522,9 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="I3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -535,11 +533,11 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="9"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
+  <dataConsolidate/>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{F961C31A-7DF1-4C7B-B510-64A4537383BE}">
@@ -557,10 +555,10 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{54280F5A-1049-470C-B3CF-8EB5A66C762E}">
       <formula1>"预期结果"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1" xr:uid="{07F45B15-284D-4B79-9928-951084DD206E}">
-      <formula1>"创建时间"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1" xr:uid="{31056DDF-BC0C-4CCC-B21A-3406EA1D7133}">
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="输入时间样式" error="年/月/日" promptTitle="输入时间样式" prompt="年/月/日" sqref="I1:I1048576" xr:uid="{B243B99D-3CA9-4E6E-8ADE-756E98CFD615}">
+      <formula1>45485</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="输入时间样式" error="年/月/日" promptTitle="输入时间样式" prompt="年/月/日" sqref="J1:J1048576" xr:uid="{E622156C-BFB2-482D-811F-09EDC74BA9E3}">
       <formula1>"修改时间"</formula1>
     </dataValidation>
   </dataValidations>
